--- a/internal/migration/Defab Thrippunithura/DYBL MTRL.xlsx
+++ b/internal/migration/Defab Thrippunithura/DYBL MTRL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stok Report 2025-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QMark\defab_erp_backend\internal\migration\Defab Thrippunithura\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C5EB435-9C99-4270-A890-5A9E88E3F64C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D68372-CA89-4CA2-BD15-0F9D2A5D711A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="0" windowWidth="28530" windowHeight="15465" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="7">
-  <si>
-    <t>Dybl Mtrl</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="6">
   <si>
     <t>SL .NO</t>
   </si>
@@ -372,30 +369,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:E93"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -403,7 +400,7 @@
         <v>5218</v>
       </c>
       <c r="C3" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3">
         <v>50.5</v>
@@ -412,12 +409,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>5217</v>
       </c>
       <c r="C4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>30.5</v>
@@ -426,12 +423,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>5217</v>
       </c>
       <c r="C5" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>34</v>
@@ -440,12 +437,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2804</v>
       </c>
       <c r="C6" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>30</v>
@@ -454,12 +451,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>2810</v>
       </c>
       <c r="C7" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>49.8</v>
@@ -468,12 +465,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>5218</v>
       </c>
       <c r="C8" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>41.4</v>
@@ -482,12 +479,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>5219</v>
       </c>
       <c r="C9" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>40.4</v>
@@ -496,12 +493,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>5217</v>
       </c>
       <c r="C10" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>15.3</v>
@@ -510,12 +507,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2801</v>
       </c>
       <c r="C11" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>22.35</v>
@@ -524,12 +521,12 @@
         <v>595</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>2803</v>
       </c>
       <c r="C12" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>38.700000000000003</v>
@@ -538,12 +535,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>5218</v>
       </c>
       <c r="C13" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>32</v>
@@ -552,12 +549,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5217</v>
       </c>
       <c r="C14" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>37.5</v>
@@ -566,12 +563,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>5038</v>
       </c>
       <c r="C15" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>50</v>
@@ -580,12 +577,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>2803</v>
       </c>
       <c r="C16" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>48.1</v>
@@ -594,12 +591,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>5063</v>
       </c>
       <c r="C17" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>34.9</v>
@@ -608,12 +605,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>2807</v>
       </c>
       <c r="C18" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>27.9</v>
@@ -622,12 +619,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>5063</v>
       </c>
       <c r="C19" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>46.8</v>
@@ -636,12 +633,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>2803</v>
       </c>
       <c r="C20" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>42.85</v>
@@ -650,12 +647,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>5218</v>
       </c>
       <c r="C21" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>52</v>
@@ -664,12 +661,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>5219</v>
       </c>
       <c r="C22" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>42</v>
@@ -678,12 +675,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>5219</v>
       </c>
       <c r="C23" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>41.5</v>
@@ -692,12 +689,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>2803</v>
       </c>
       <c r="C24" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>42</v>
@@ -706,12 +703,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>5219</v>
       </c>
       <c r="C25" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>41.75</v>
@@ -720,12 +717,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>5218</v>
       </c>
       <c r="C26" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>40</v>
@@ -734,12 +731,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>2799</v>
       </c>
       <c r="C27" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>29.5</v>
@@ -748,12 +745,12 @@
         <v>470</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>5217</v>
       </c>
       <c r="C28" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>37</v>
@@ -762,12 +759,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>5218</v>
       </c>
       <c r="C29" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>35.5</v>
@@ -776,12 +773,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>5219</v>
       </c>
       <c r="C30" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>34.549999999999997</v>
@@ -790,12 +787,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>2799</v>
       </c>
       <c r="C31" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>38.799999999999997</v>
@@ -804,12 +801,12 @@
         <v>470</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>5035</v>
       </c>
       <c r="C32" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>73</v>
@@ -818,12 +815,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>2805</v>
       </c>
       <c r="C33" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>50</v>
@@ -832,12 +829,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>5063</v>
       </c>
       <c r="C34" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>63</v>
@@ -846,12 +843,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>2807</v>
       </c>
       <c r="C35" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>46.25</v>
@@ -860,12 +857,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>2804</v>
       </c>
       <c r="C36" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>50</v>
@@ -874,12 +871,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>5219</v>
       </c>
       <c r="C37" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>42</v>
@@ -888,12 +885,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>3343</v>
       </c>
       <c r="C38" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>12.9</v>
@@ -902,12 +899,12 @@
         <v>490</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>4219</v>
       </c>
       <c r="C39" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>42</v>
@@ -916,12 +913,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>5063</v>
       </c>
       <c r="C40" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>22</v>
@@ -930,12 +927,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>5063</v>
       </c>
       <c r="C41" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>32</v>
@@ -944,12 +941,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>5063</v>
       </c>
       <c r="C42" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>38</v>
@@ -958,12 +955,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>2803</v>
       </c>
       <c r="C43" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>18.5</v>
@@ -972,12 +969,12 @@
         <v>255</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>2810</v>
       </c>
       <c r="C44" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>13</v>
@@ -986,12 +983,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1535</v>
       </c>
       <c r="C45" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>16</v>
@@ -1000,12 +997,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>1535</v>
       </c>
       <c r="C46" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>11.4</v>
@@ -1014,12 +1011,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1535</v>
       </c>
       <c r="C47" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>12.85</v>
@@ -1028,12 +1025,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>1535</v>
       </c>
       <c r="C48" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>12.85</v>
@@ -1042,12 +1039,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>2800</v>
       </c>
       <c r="C49" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>36.75</v>
@@ -1056,12 +1053,12 @@
         <v>565</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1538</v>
       </c>
       <c r="C50" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>17.2</v>
@@ -1070,12 +1067,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D51">
         <v>6.3</v>
@@ -1084,12 +1081,12 @@
         <v>455</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>5038</v>
       </c>
       <c r="C52" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D52">
         <v>37</v>
@@ -1098,12 +1095,12 @@
         <v>350</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>5588</v>
       </c>
       <c r="C53" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>35.700000000000003</v>
@@ -1112,12 +1109,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>3254</v>
       </c>
       <c r="C54" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>16</v>
@@ -1126,12 +1123,12 @@
         <v>410</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>1449</v>
       </c>
       <c r="C55" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>50</v>
@@ -1140,12 +1137,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>5218</v>
       </c>
       <c r="C56" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D56">
         <v>41</v>
@@ -1154,12 +1151,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>3122</v>
       </c>
       <c r="C57" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>44.7</v>
@@ -1168,12 +1165,12 @@
         <v>635</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>3283</v>
       </c>
       <c r="C58" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D58">
         <v>37</v>
@@ -1182,12 +1179,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>1333</v>
       </c>
       <c r="C59" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>47.5</v>
@@ -1196,12 +1193,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>3234</v>
       </c>
       <c r="C60" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>65.900000000000006</v>
@@ -1210,12 +1207,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>5219</v>
       </c>
       <c r="C61" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>41.5</v>
@@ -1224,12 +1221,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>5218</v>
       </c>
       <c r="C62" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D62">
         <v>41.75</v>
@@ -1238,12 +1235,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>872</v>
       </c>
       <c r="C63" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D63">
         <v>49.75</v>
@@ -1252,12 +1249,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>2805</v>
       </c>
       <c r="C64" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>8</v>
@@ -1266,12 +1263,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>2805</v>
       </c>
       <c r="C65" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>40.4</v>
@@ -1280,12 +1277,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>2831</v>
       </c>
       <c r="C66" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D66">
         <v>17.399999999999999</v>
@@ -1294,12 +1291,12 @@
         <v>495</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>3143</v>
       </c>
       <c r="C67" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D67">
         <v>15.1</v>
@@ -1308,12 +1305,12 @@
         <v>510</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>5037</v>
       </c>
       <c r="C68" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>9.4</v>
@@ -1322,12 +1319,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>274</v>
       </c>
       <c r="C69" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>10</v>
@@ -1336,12 +1333,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>3252</v>
       </c>
       <c r="C70" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D70">
         <v>5.7</v>
@@ -1350,12 +1347,12 @@
         <v>360</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>3213</v>
       </c>
       <c r="C71" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D71">
         <v>50</v>
@@ -1364,12 +1361,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>2932</v>
       </c>
       <c r="C72" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72">
         <v>20.56</v>
@@ -1378,12 +1375,12 @@
         <v>620</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>2811</v>
       </c>
       <c r="C73" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D73">
         <v>47.9</v>
@@ -1392,12 +1389,12 @@
         <v>340</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>3238</v>
       </c>
       <c r="C74" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>20</v>
@@ -1406,12 +1403,12 @@
         <v>445</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>3341</v>
       </c>
       <c r="C75" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D75">
         <v>28.8</v>
@@ -1420,12 +1417,12 @@
         <v>655</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>2878</v>
       </c>
       <c r="C76" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>10</v>
@@ -1434,12 +1431,12 @@
         <v>635</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>2807</v>
       </c>
       <c r="C77" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D77">
         <v>47.2</v>
@@ -1448,12 +1445,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>2934</v>
       </c>
       <c r="C78" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D78">
         <v>20</v>
@@ -1462,12 +1459,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>2928</v>
       </c>
       <c r="C79" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>37</v>
@@ -1476,12 +1473,12 @@
         <v>625</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>3245</v>
       </c>
       <c r="C80" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D80">
         <v>21</v>
@@ -1490,12 +1487,12 @@
         <v>750</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>3344</v>
       </c>
       <c r="C81" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D81">
         <v>21</v>
@@ -1504,12 +1501,12 @@
         <v>950</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>2773</v>
       </c>
       <c r="C82" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>20</v>
@@ -1518,12 +1515,12 @@
         <v>595</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>2808</v>
       </c>
       <c r="C83" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D83">
         <v>54.5</v>
@@ -1532,12 +1529,12 @@
         <v>370</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>2780</v>
       </c>
       <c r="C84" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>18</v>
@@ -1546,12 +1543,12 @@
         <v>900</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>1528</v>
       </c>
       <c r="C85" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>20</v>
@@ -1560,12 +1557,12 @@
         <v>395</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>4337</v>
       </c>
       <c r="C86" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D86">
         <v>22.5</v>
@@ -1574,12 +1571,12 @@
         <v>495</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>2930</v>
       </c>
       <c r="C87" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D87">
         <v>33.299999999999997</v>
@@ -1588,12 +1585,12 @@
         <v>510</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D88">
         <v>16.3</v>
@@ -1602,12 +1599,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>2778</v>
       </c>
       <c r="C89" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>20.75</v>
@@ -1616,12 +1613,12 @@
         <v>430</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>3388</v>
       </c>
       <c r="C90" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D90">
         <v>20.8</v>
@@ -1630,12 +1627,12 @@
         <v>410</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>3250</v>
       </c>
       <c r="C91" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D91">
         <v>18.600000000000001</v>
@@ -1644,12 +1641,12 @@
         <v>995</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>276</v>
       </c>
       <c r="C92" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D92">
         <v>10</v>
@@ -1658,28 +1655,18 @@
         <v>475</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>206</v>
       </c>
       <c r="C93" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>29</v>
       </c>
       <c r="E93">
         <v>190</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C94" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C95" t="s">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1690,35 +1677,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{793928C9-9A63-4F00-8C61-5F5BBE767E80}">
   <dimension ref="A2:E96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>25.75</v>
@@ -1727,12 +1714,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>22</v>
@@ -1741,12 +1728,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>5624</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6">
         <v>26</v>
@@ -1755,12 +1742,12 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>25.25</v>
@@ -1769,12 +1756,12 @@
         <v>435</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>35</v>
@@ -1783,12 +1770,12 @@
         <v>435</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>1822</v>
       </c>
       <c r="C9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>20.3</v>
@@ -1797,12 +1784,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>1821</v>
       </c>
       <c r="C10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10">
         <v>20.100000000000001</v>
@@ -1811,12 +1798,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>5662</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11">
         <v>32</v>
@@ -1825,12 +1812,12 @@
         <v>160</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>3357</v>
       </c>
       <c r="C12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>23.25</v>
@@ -1839,12 +1826,12 @@
         <v>575</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13">
         <v>26.75</v>
@@ -1853,12 +1840,12 @@
         <v>440</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>5624</v>
       </c>
       <c r="C14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14">
         <v>27</v>
@@ -1867,12 +1854,12 @@
         <v>315</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>19</v>
@@ -1881,12 +1868,12 @@
         <v>315</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>1301</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D16">
         <v>22</v>
@@ -1895,12 +1882,12 @@
         <v>525</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17">
         <v>27.25</v>
@@ -1909,12 +1896,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>1821</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18">
         <v>23.5</v>
@@ -1923,12 +1910,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>5627</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>26.5</v>
@@ -1937,12 +1924,12 @@
         <v>395</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>5627</v>
       </c>
       <c r="C20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>26.5</v>
@@ -1951,12 +1938,12 @@
         <v>395</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>970</v>
       </c>
       <c r="C21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>22.25</v>
@@ -1965,12 +1952,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>5668</v>
       </c>
       <c r="C22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>36.85</v>
@@ -1979,12 +1966,12 @@
         <v>215</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>5966</v>
       </c>
       <c r="C23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>10.5</v>
@@ -1993,12 +1980,12 @@
         <v>455</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>26</v>
@@ -2007,12 +1994,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>875</v>
       </c>
       <c r="C25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>20.75</v>
@@ -2021,12 +2008,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>3239</v>
       </c>
       <c r="C26" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26">
         <v>50</v>
@@ -2035,12 +2022,12 @@
         <v>265</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>5626</v>
       </c>
       <c r="C27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>22</v>
@@ -2049,12 +2036,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>5626</v>
       </c>
       <c r="C28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D28">
         <v>23.5</v>
@@ -2063,12 +2050,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>5626</v>
       </c>
       <c r="C29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>25</v>
@@ -2077,12 +2064,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>969</v>
       </c>
       <c r="C30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30">
         <v>18.25</v>
@@ -2091,12 +2078,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>1821</v>
       </c>
       <c r="C31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31">
         <v>10.65</v>
@@ -2105,12 +2092,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>1831</v>
       </c>
       <c r="C32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>16.75</v>
@@ -2119,12 +2106,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1299</v>
       </c>
       <c r="C33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
         <v>17.600000000000001</v>
@@ -2133,12 +2120,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>5626</v>
       </c>
       <c r="C34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
         <v>25.6</v>
@@ -2147,12 +2134,12 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>1830</v>
       </c>
       <c r="C35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
         <v>10.8</v>
@@ -2161,12 +2148,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>1833</v>
       </c>
       <c r="C36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>22.15</v>
@@ -2175,12 +2162,12 @@
         <v>345</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>1300</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>19.25</v>
@@ -2189,12 +2176,12 @@
         <v>125</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>1842</v>
       </c>
       <c r="C38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>20.8</v>
@@ -2203,12 +2190,12 @@
         <v>865</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>5966</v>
       </c>
       <c r="C39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>10.5</v>
@@ -2217,12 +2204,12 @@
         <v>455</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>474</v>
       </c>
       <c r="C40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>24.5</v>
@@ -2231,12 +2218,12 @@
         <v>295</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>1839</v>
       </c>
       <c r="C41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>13.65</v>
@@ -2245,12 +2232,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>1821</v>
       </c>
       <c r="C42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D42">
         <v>19</v>
@@ -2259,12 +2246,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>873</v>
       </c>
       <c r="C43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43">
         <v>5.25</v>
@@ -2273,12 +2260,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>5219</v>
       </c>
       <c r="C44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D44">
         <v>21.4</v>
@@ -2287,12 +2274,12 @@
         <v>375</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1761</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -2301,12 +2288,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>873</v>
       </c>
       <c r="C46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46">
         <v>4.2</v>
@@ -2315,12 +2302,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1821</v>
       </c>
       <c r="C47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D47">
         <v>10</v>
@@ -2329,12 +2316,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48">
         <v>4.9000000000000004</v>
@@ -2343,12 +2330,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>1829</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49">
         <v>15</v>
@@ -2357,12 +2344,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1821</v>
       </c>
       <c r="C50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50">
         <v>13.45</v>
@@ -2371,12 +2358,12 @@
         <v>175</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>3342</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51">
         <v>14.7</v>
@@ -2385,12 +2372,12 @@
         <v>210</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>2808</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52">
         <v>54.5</v>
@@ -2399,12 +2386,12 @@
         <v>370</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>2936</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53">
         <v>32.5</v>
@@ -2413,12 +2400,12 @@
         <v>825</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>2931</v>
       </c>
       <c r="C54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54">
         <v>30.5</v>
@@ -2427,12 +2414,12 @@
         <v>825</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>3241</v>
       </c>
       <c r="C55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55">
         <v>21</v>
@@ -2441,12 +2428,12 @@
         <v>735</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>2775</v>
       </c>
       <c r="C56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56">
         <v>20.45</v>
@@ -2455,12 +2442,12 @@
         <v>865</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>2772</v>
       </c>
       <c r="C57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D57">
         <v>20</v>
@@ -2469,12 +2456,12 @@
         <v>565</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>3144</v>
       </c>
       <c r="C58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D58">
         <v>12.4</v>
@@ -2483,12 +2470,12 @@
         <v>865</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>3386</v>
       </c>
       <c r="C59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D59">
         <v>15</v>
@@ -2497,12 +2484,12 @@
         <v>585</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>3255</v>
       </c>
       <c r="C60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D60">
         <v>16</v>
@@ -2511,12 +2498,12 @@
         <v>580</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>3247</v>
       </c>
       <c r="C61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D61">
         <v>20.100000000000001</v>
@@ -2525,12 +2512,12 @@
         <v>795</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>3234</v>
       </c>
       <c r="C62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D62">
         <v>49.2</v>
@@ -2539,12 +2526,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>3236</v>
       </c>
       <c r="C63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63">
         <v>37.5</v>
@@ -2553,12 +2540,12 @@
         <v>250</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>3244</v>
       </c>
       <c r="C64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64">
         <v>10</v>
@@ -2567,12 +2554,12 @@
         <v>645</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>3238</v>
       </c>
       <c r="C65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65">
         <v>30</v>
@@ -2581,12 +2568,12 @@
         <v>445</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>3243</v>
       </c>
       <c r="C66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66">
         <v>20.8</v>
@@ -2595,12 +2582,12 @@
         <v>675</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>1793</v>
       </c>
       <c r="C67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67">
         <v>22.5</v>
@@ -2609,12 +2596,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>1458</v>
       </c>
       <c r="C68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D68">
         <v>50</v>
@@ -2623,12 +2610,12 @@
         <v>220</v>
       </c>
     </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>3238</v>
       </c>
       <c r="C69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D69">
         <v>21.2</v>
@@ -2637,12 +2624,12 @@
         <v>445</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>3234</v>
       </c>
       <c r="C70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D70">
         <v>29</v>
@@ -2651,12 +2638,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>1837</v>
       </c>
       <c r="C71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D71">
         <v>23</v>
@@ -2665,12 +2652,12 @@
         <v>70</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>1793</v>
       </c>
       <c r="C72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D72">
         <v>31</v>
@@ -2679,12 +2666,12 @@
         <v>195</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B73" s="1">
         <v>3161</v>
       </c>
       <c r="C73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D73" s="1">
         <v>31</v>
@@ -2693,12 +2680,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>2774</v>
       </c>
       <c r="C74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D74">
         <v>17.7</v>
@@ -2707,12 +2694,12 @@
         <v>775</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>1132</v>
       </c>
       <c r="C75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75">
         <v>50</v>
@@ -2721,12 +2708,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>2807</v>
       </c>
       <c r="C76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76">
         <v>33.65</v>
@@ -2735,12 +2722,12 @@
         <v>290</v>
       </c>
     </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>3235</v>
       </c>
       <c r="C77" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D77">
         <v>50</v>
@@ -2749,12 +2736,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>1836</v>
       </c>
       <c r="C78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D78">
         <v>25</v>
@@ -2763,12 +2750,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>2771</v>
       </c>
       <c r="C79" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D79">
         <v>14.75</v>
@@ -2777,12 +2764,12 @@
         <v>475</v>
       </c>
     </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>1131</v>
       </c>
       <c r="C80" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D80">
         <v>30.15</v>
@@ -2791,12 +2778,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>1131</v>
       </c>
       <c r="C81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81">
         <v>50</v>
@@ -2805,12 +2792,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>3240</v>
       </c>
       <c r="C82" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82">
         <v>21</v>
@@ -2819,12 +2806,12 @@
         <v>765</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>3242</v>
       </c>
       <c r="C83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83">
         <v>20</v>
@@ -2833,12 +2820,12 @@
         <v>845</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>3242</v>
       </c>
       <c r="C84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D84">
         <v>21</v>
@@ -2847,12 +2834,12 @@
         <v>845</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>174</v>
       </c>
       <c r="C85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85">
         <v>36</v>
@@ -2861,12 +2848,12 @@
         <v>225</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>2935</v>
       </c>
       <c r="C86" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86">
         <v>20</v>
@@ -2875,12 +2862,12 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>3253</v>
       </c>
       <c r="C87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87">
         <v>20</v>
@@ -2889,12 +2876,12 @@
         <v>675</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>3340</v>
       </c>
       <c r="C88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D88">
         <v>19.5</v>
@@ -2903,12 +2890,12 @@
         <v>480</v>
       </c>
     </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>8108</v>
       </c>
       <c r="C89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D89">
         <v>45.25</v>
@@ -2917,12 +2904,12 @@
         <v>155</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>1453</v>
       </c>
       <c r="C90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D90">
         <v>45</v>
@@ -2931,12 +2918,12 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>4377</v>
       </c>
       <c r="C91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D91">
         <v>31</v>
@@ -2945,12 +2932,12 @@
         <v>275</v>
       </c>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>1460</v>
       </c>
       <c r="C92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D92">
         <v>50</v>
@@ -2959,12 +2946,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>5242</v>
       </c>
       <c r="C93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>91.3</v>
@@ -2973,12 +2960,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>3128</v>
       </c>
       <c r="C94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D94">
         <v>102.25</v>
@@ -2987,12 +2974,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>1461</v>
       </c>
       <c r="C95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D95">
         <v>50</v>
@@ -3001,12 +2988,12 @@
         <v>285</v>
       </c>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>5242</v>
       </c>
       <c r="C96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>84</v>
@@ -3023,35 +3010,38 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24107CE0-6E4E-4945-83B7-27746F8B6C78}">
   <dimension ref="A2:E53"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>872</v>
       </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
       <c r="D3">
         <v>50</v>
       </c>
@@ -3059,10 +3049,13 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>872</v>
       </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
       <c r="D4">
         <v>50.25</v>
       </c>
@@ -3070,10 +3063,13 @@
         <v>115</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>872</v>
       </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
       <c r="D5">
         <v>24.35</v>
       </c>
@@ -3081,10 +3077,13 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2782</v>
       </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
       <c r="D6">
         <v>14.75</v>
       </c>
@@ -3092,10 +3091,13 @@
         <v>315</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>872</v>
       </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
       <c r="D7">
         <v>39.6</v>
       </c>
@@ -3103,10 +3105,13 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>3334</v>
       </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
       <c r="D8">
         <v>13.3</v>
       </c>
@@ -3114,10 +3119,13 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>2805</v>
       </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
       <c r="D9">
         <v>44</v>
       </c>
@@ -3125,10 +3133,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>3251</v>
       </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
       <c r="D10">
         <v>21</v>
       </c>
@@ -3136,10 +3147,13 @@
         <v>305</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>2805</v>
       </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
       <c r="D11">
         <v>53.25</v>
       </c>
@@ -3147,10 +3161,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>3111</v>
       </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
       <c r="D12">
         <v>7.75</v>
       </c>
@@ -3158,10 +3175,13 @@
         <v>220</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>2809</v>
       </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
       <c r="D13">
         <v>48.8</v>
       </c>
@@ -3169,10 +3189,13 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>3111</v>
       </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
       <c r="D14">
         <v>7.8</v>
       </c>
@@ -3180,10 +3203,13 @@
         <v>220</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>1841</v>
       </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
       <c r="D15">
         <v>38.799999999999997</v>
       </c>
@@ -3191,10 +3217,13 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>3249</v>
       </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
       <c r="D16">
         <v>17</v>
       </c>
@@ -3202,10 +3231,13 @@
         <v>495</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>1335</v>
       </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
       <c r="D17">
         <v>43.8</v>
       </c>
@@ -3213,10 +3245,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>3114</v>
       </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
       <c r="D18">
         <v>68</v>
       </c>
@@ -3224,10 +3259,13 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>5039</v>
       </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
       <c r="D19">
         <v>58</v>
       </c>
@@ -3235,10 +3273,13 @@
         <v>210</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>1128</v>
       </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
       <c r="D20">
         <v>47.3</v>
       </c>
@@ -3246,10 +3287,13 @@
         <v>225</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>3126</v>
       </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
       <c r="D21">
         <v>43.8</v>
       </c>
@@ -3257,10 +3301,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>5040</v>
       </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
       <c r="D22">
         <v>75</v>
       </c>
@@ -3268,10 +3315,13 @@
         <v>190</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>42</v>
       </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
       <c r="D23">
         <v>22.25</v>
       </c>
@@ -3279,10 +3329,13 @@
         <v>835</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>1454</v>
       </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
       <c r="D24">
         <v>50</v>
       </c>
@@ -3290,10 +3343,13 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>3230</v>
       </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
       <c r="D25">
         <v>2.4</v>
       </c>
@@ -3301,10 +3357,13 @@
         <v>350</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>3120</v>
       </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
       <c r="D26">
         <v>52</v>
       </c>
@@ -3312,10 +3371,13 @@
         <v>225</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>3113</v>
       </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
       <c r="D27">
         <v>23.8</v>
       </c>
@@ -3323,10 +3385,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>1457</v>
       </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
       <c r="D28">
         <v>46</v>
       </c>
@@ -3334,10 +3399,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>5037</v>
       </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
       <c r="D29">
         <v>43</v>
       </c>
@@ -3345,10 +3413,13 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>3124</v>
       </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
       <c r="D30">
         <v>58.75</v>
       </c>
@@ -3356,10 +3427,13 @@
         <v>220</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>3117</v>
       </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
       <c r="D31">
         <v>37.5</v>
       </c>
@@ -3367,10 +3441,13 @@
         <v>230</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>3109</v>
       </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
       <c r="D32">
         <v>34.25</v>
       </c>
@@ -3378,10 +3455,13 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>1835</v>
       </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
       <c r="D33">
         <v>11</v>
       </c>
@@ -3389,10 +3469,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>1294</v>
       </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
       <c r="D34">
         <v>51.65</v>
       </c>
@@ -3400,10 +3483,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>3117</v>
       </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
       <c r="D35">
         <v>42.4</v>
       </c>
@@ -3411,10 +3497,13 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>3161</v>
       </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
       <c r="D36">
         <v>38.25</v>
       </c>
@@ -3422,10 +3511,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>1455</v>
       </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
       <c r="D37">
         <v>46.7</v>
       </c>
@@ -3433,10 +3525,13 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>1459</v>
       </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
       <c r="D38">
         <v>50</v>
       </c>
@@ -3444,10 +3539,13 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>1294</v>
       </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
       <c r="D39">
         <v>14</v>
       </c>
@@ -3455,10 +3553,13 @@
         <v>95</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>3110</v>
       </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
       <c r="D40">
         <v>24.75</v>
       </c>
@@ -3466,10 +3567,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>2808</v>
       </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
       <c r="D41">
         <v>6.5</v>
       </c>
@@ -3477,10 +3581,13 @@
         <v>370</v>
       </c>
     </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>2809</v>
       </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
       <c r="D42">
         <v>50</v>
       </c>
@@ -3488,10 +3595,13 @@
         <v>240</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>474</v>
       </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
       <c r="D43">
         <v>25.75</v>
       </c>
@@ -3499,10 +3609,13 @@
         <v>295</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>1593</v>
       </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
       <c r="D44">
         <v>3.5</v>
       </c>
@@ -3510,10 +3623,13 @@
         <v>475</v>
       </c>
     </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>1592</v>
       </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
       <c r="D45">
         <v>7</v>
       </c>
@@ -3521,10 +3637,13 @@
         <v>450</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>1835</v>
       </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
       <c r="D46">
         <v>9.8000000000000007</v>
       </c>
@@ -3532,10 +3651,13 @@
         <v>155</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>1330</v>
       </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
       <c r="D47">
         <v>44</v>
       </c>
@@ -3543,10 +3665,13 @@
         <v>195</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>3235</v>
       </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
       <c r="D48">
         <v>48.5</v>
       </c>
@@ -3554,10 +3679,13 @@
         <v>295</v>
       </c>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>3119</v>
       </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
       <c r="D49">
         <v>30.3</v>
       </c>
@@ -3565,10 +3693,13 @@
         <v>545</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>1452</v>
       </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
       <c r="D50">
         <v>35.950000000000003</v>
       </c>
@@ -3576,10 +3707,13 @@
         <v>195</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>3234</v>
       </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
       <c r="D51">
         <v>7.25</v>
       </c>
@@ -3587,10 +3721,13 @@
         <v>275</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>3339</v>
       </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
       <c r="D52">
         <v>21</v>
       </c>
@@ -3598,9 +3735,12 @@
         <v>495</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>5220</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
       </c>
       <c r="D53">
         <v>15</v>
